--- a/templates/record_billing.xlsx
+++ b/templates/record_billing.xlsx
@@ -1,42 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/congdat/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/congdat/Developer/lab-admin-go/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{67C4ED10-E469-BD49-9E10-6F416AC997B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C31DEC91-87EA-5D41-8DE9-D0C728F0F900}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8580" yWindow="3600" windowWidth="28040" windowHeight="17440" xr2:uid="{5A0C30C7-8D42-874F-AF07-D509C72B7223}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>PHÒNG XÉT NGHIỆM Y KHOA ANH QUÂN</t>
   </si>
@@ -53,12 +37,12 @@
     <t>Họ tên</t>
   </si>
   <si>
+    <t>Tuổi</t>
+  </si>
+  <si>
     <t>Địa chỉ</t>
   </si>
   <si>
-    <t>Tuổi</t>
-  </si>
-  <si>
     <t>STT</t>
   </si>
   <si>
@@ -72,43 +56,67 @@
   </si>
   <si>
     <t>Thành tiền</t>
+  </si>
+  <si>
+    <t>Ký tên</t>
+  </si>
+  <si>
+    <t>Nguyễn Công Mẫn</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
     <font>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="20"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow (Body)"/>
-    </font>
-    <font>
-      <sz val="22"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow (Body)"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -119,7 +127,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -129,16 +137,29 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -146,22 +167,42 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -181,150 +222,56 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Sheets">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4285F4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="EA4335"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="FBBC04"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="34A853"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="FF6D01"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="46BDC6"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="1155CC"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="1155CC"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -386,6 +333,13 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -394,13 +348,6 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -465,117 +412,160 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB5FAF33-9E6B-9740-B000-0ACABE8C833F}">
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="2" max="2" width="55.6640625" customWidth="1"/>
+    <col min="1" max="1" width="7.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="38.1640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.33203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.1640625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="12.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="27" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-    </row>
-    <row r="2" spans="1:5" ht="19" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+    </row>
+    <row r="2" spans="1:5" ht="31" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-    </row>
-    <row r="3" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+    </row>
+    <row r="3" spans="1:5" ht="44" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+    </row>
+    <row r="4" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+    </row>
+    <row r="5" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:5" ht="13" x14ac:dyDescent="0.15">
+      <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C6" t="s">
+      <c r="B6" s="3"/>
+      <c r="C6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+    </row>
+    <row r="7" spans="1:5" ht="13" x14ac:dyDescent="0.15">
+      <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+    </row>
+    <row r="8" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="13" t="s">
         <v>11</v>
       </c>
     </row>
+    <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+    </row>
+    <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+    </row>
+    <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+    </row>
+    <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+    </row>
+    <row r="17" spans="3:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C17" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="7">
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="C13:E16"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="A4:E4"/>
+    <mergeCell ref="C12:E12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="92" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/templates/record_billing.xlsx
+++ b/templates/record_billing.xlsx
@@ -8,14 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/congdat/Developer/lab-admin-go/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C31DEC91-87EA-5D41-8DE9-D0C728F0F900}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED87A533-5830-C647-AC13-656A46798E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6340" yWindow="1640" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -37,9 +49,6 @@
     <t>Họ tên</t>
   </si>
   <si>
-    <t>Tuổi</t>
-  </si>
-  <si>
     <t>Địa chỉ</t>
   </si>
   <si>
@@ -62,6 +71,9 @@
   </si>
   <si>
     <t>Nguyễn Công Mẫn</t>
+  </si>
+  <si>
+    <t>Năm sinh</t>
   </si>
 </sst>
 </file>
@@ -167,7 +179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -195,14 +207,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -478,22 +487,18 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:5" ht="13" x14ac:dyDescent="0.15">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="3"/>
+    </row>
+    <row r="7" spans="1:5" ht="13" x14ac:dyDescent="0.15">
+      <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-    </row>
-    <row r="7" spans="1:5" ht="13" x14ac:dyDescent="0.15">
-      <c r="A7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
     </row>
@@ -505,25 +510,25 @@
       <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="C9" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="D9" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="E9" s="14" t="s">
         <v>10</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C12" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
@@ -550,7 +555,7 @@
     </row>
     <row r="17" spans="3:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C17" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>

--- a/templates/record_billing.xlsx
+++ b/templates/record_billing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/congdat/Developer/lab-admin-go/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED87A533-5830-C647-AC13-656A46798E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28C77789-50B4-3F42-AFBA-64B58497E9BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6340" yWindow="1640" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>PHÒNG XÉT NGHIỆM Y KHOA ANH QUÂN</t>
   </si>
@@ -46,41 +46,62 @@
     <t>Ngày: 16/02/2025</t>
   </si>
   <si>
-    <t>Họ tên</t>
-  </si>
-  <si>
-    <t>Địa chỉ</t>
-  </si>
-  <si>
-    <t>STT</t>
-  </si>
-  <si>
-    <t>Tên hàng hoá, dịch vụ</t>
-  </si>
-  <si>
-    <t>Số lượng</t>
-  </si>
-  <si>
-    <t>Đơn giá</t>
-  </si>
-  <si>
-    <t>Thành tiền</t>
-  </si>
-  <si>
-    <t>Ký tên</t>
-  </si>
-  <si>
-    <t>Nguyễn Công Mẫn</t>
-  </si>
-  <si>
-    <t>Năm sinh</t>
+    <t>STT
+(No)</t>
+  </si>
+  <si>
+    <t>TÊN XÉT NGHIỆM
+(Test)</t>
+  </si>
+  <si>
+    <t>SỐ LƯỢNG
+(Quanity)</t>
+  </si>
+  <si>
+    <t>ĐƠN GIÁ
+(Unit price)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Thành tiền</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+(Amount)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Tổng tiền thanh toán: </t>
+  </si>
+  <si>
+    <t>Họ tên:</t>
+  </si>
+  <si>
+    <t>Địa chỉ:</t>
+  </si>
+  <si>
+    <t>Năm sinh:</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -89,43 +110,58 @@
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="22"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="13"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -139,7 +175,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -149,29 +185,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -179,38 +202,50 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -432,145 +467,154 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="7.5" style="1" customWidth="1"/>
-    <col min="2" max="2" width="38.1640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16.33203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.1640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10.83203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="40.83203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" style="1" customWidth="1"/>
+    <col min="4" max="5" width="20.83203125" style="1" customWidth="1"/>
     <col min="6" max="16384" width="12.6640625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-    </row>
-    <row r="2" spans="1:5" ht="31" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="8" t="s">
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+    </row>
+    <row r="2" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
     </row>
     <row r="3" spans="1:5" ht="44" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-    </row>
-    <row r="4" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" s="12" t="s">
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+    </row>
+    <row r="4" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-    </row>
-    <row r="5" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+    </row>
+    <row r="5" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="1:5" ht="13" x14ac:dyDescent="0.15">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="17"/>
+      <c r="C6" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="16"/>
+      <c r="E6" s="15"/>
+    </row>
+    <row r="7" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="15"/>
+    </row>
+    <row r="8" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+    </row>
+    <row r="9" spans="1:5" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="3"/>
-    </row>
-    <row r="7" spans="1:5" ht="13" x14ac:dyDescent="0.15">
-      <c r="A7" s="1" t="s">
+      <c r="B9" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-    </row>
-    <row r="8" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="13" t="s">
+      <c r="C9" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="D9" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="E9" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="14" t="s">
+    </row>
+    <row r="10" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="10"/>
+    </row>
+    <row r="11" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="14" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C12" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-    </row>
-    <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-    </row>
-    <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-    </row>
-    <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-    </row>
-    <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-    </row>
-    <row r="17" spans="3:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C17" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-    </row>
+      <c r="D11" s="14"/>
+      <c r="E11" s="18"/>
+    </row>
+    <row r="12" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="13" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="14" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="15" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="16" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="17" ht="20" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="18" ht="20" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="19" ht="20" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="20" ht="20" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="21" ht="20" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="22" ht="20" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="23" ht="20" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="24" ht="20" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="25" ht="20" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="26" ht="20" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="27" ht="20" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="28" ht="20" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="29" ht="20" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="30" ht="20" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="31" ht="20" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="32" ht="20" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="33" ht="20" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="34" ht="20" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="35" ht="20" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="36" ht="20" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="37" ht="20" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="C13:E16"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C11:D11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="92" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup paperSize="9" scale="75" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>